--- a/docs/files/REPORT_FILTRI/Agente - CR PACI CLAUDIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR PACI CLAUDIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,10 +676,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>1</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>1</v>
@@ -829,16 +829,16 @@
         <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR PACI CLAUDIO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR PACI CLAUDIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -838,7 +838,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
